--- a/excel/EDS-Lab-Data-PowerApps.xlsx
+++ b/excel/EDS-Lab-Data-PowerApps.xlsx
@@ -30,11 +30,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.###"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -164,7 +163,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -242,8 +241,12 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -559,8 +562,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblSettings" displayName="tblSettings" ref="A1:C12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblSettings" displayName="tblSettings" ref="A1:C15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C15"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Key"/>
     <tableColumn id="2" name="Value"/>
@@ -1261,124 +1264,124 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE-INV</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE row (keeps column types)</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="R2" s="27" t="n">
+      <c r="R2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="S2" s="27" t="n">
+      <c r="S2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="T2" s="27" t="n">
+      <c r="T2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2" s="12" t="n">
         <v>200.5</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2" s="12" t="n">
         <v>1.5</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
@@ -1484,59 +1487,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE row (keeps column types)</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="12" t="n">
         <v>1.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE-PR</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>RECEIVED</t>
         </is>
       </c>
-      <c r="K2" s="27" t="n">
+      <c r="K2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="L2" s="27" t="n">
+      <c r="L2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
@@ -1618,41 +1621,41 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE row (keeps column types)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="D2" s="27" t="n">
+      <c r="D2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F2" s="27" t="n">
+      <c r="F2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
@@ -1806,101 +1809,101 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE-REQ-00000</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>sample@jcb.com</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE row (keeps column types)</t>
         </is>
       </c>
-      <c r="F2" s="27" t="n">
+      <c r="F2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Proto</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="27" t="n">
+      <c r="P2" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE row - Power Apps ignores rows whose key starts with SAMPLE. Do not delete.</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>2026-01-01T12:00:00</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -2000,52 +2003,52 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE-REQ-00000</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE row (keeps column types)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="12" t="n">
         <v>1.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
@@ -2065,84 +2068,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B13"/>
+  <dimension ref="B1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" style="13" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>THIS COPY IS FOR THE POWER APPS VERSION OF THE PORTAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Keep it on OneDrive for Business or a SharePoint document library. Power Apps reads and writes it through the</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Excel Online (Business) connector. It is a separate file from the one the HTA uses on the lab PC.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Rows whose first column starts with SAMPLE are there on purpose: Power Apps works out whether a column holds</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>text, numbers or dates from the data in it, and an empty table makes every column text. The app ignores</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>every SAMPLE row. Leave them in.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Users has an extra Email column on the right. Leave it blank if each person's Username is the part of their</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>email address before the @ (gaurav.shelke for gaurav.shelke@jcb.com). Fill it only when that is not true.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>When Power Apps first connects it adds a hidden __PowerAppsId__ column to each table. That is normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>ROLES: one person can hold several roles. Write them in the Role cell separated by commas, for example</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>'Engineer, Manager'. The first one is the usual role. Lab Lead and Lab Admin can view every role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>DATA HEALTH: the three Excel* rows at the bottom of Settings are formulas. Leave them; the app compares them</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>with what it read (About &gt; Data Health).</t>
         </is>
       </c>
     </row>
@@ -59295,7 +59330,7 @@
           <t>PasswordSetOn</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
@@ -61458,7 +61493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="12" min="1" max="1"/>
@@ -61639,6 +61674,54 @@
       <c r="C12" s="16" t="inlineStr">
         <is>
           <t>How many sign-offs a PR/PO needs before Approved. BUSINESS DECISION REQUIRED — set to your real number</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>ExcelPartRows</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>ROWS(tblParts)</f>
+        <v/>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Data Health: rows in Parts, counted by Excel. Do not edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>ExcelMovementRows</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>ROWS(tblMoves)</f>
+        <v/>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Data Health: rows in Movements, counted by Excel. Do not edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>ExcelStockTotal</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>SUMPRODUCT((tblMoves[Type]="RECEIPT")+(tblMoves[Type]="RETURN")+(tblMoves[Type]="ADJUST+")-(tblMoves[Type]="ISSUE")-(tblMoves[Type]="SCRAP")-(tblMoves[Type]="ADJUST-"),ABS(tblMoves[Qty]))</f>
+        <v/>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Data Health: total stock of all parts = signed sum of Movements. Do not edit.</t>
         </is>
       </c>
     </row>
@@ -62001,91 +62084,91 @@
       <c r="P6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE-PR</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE row (keeps column types)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>MATERIAL</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I7" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE-PO</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="N7" s="27" t="n">
+      <c r="N7" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="O7" s="27" t="n">
+      <c r="O7" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" s="12" t="inlineStr">
         <is>
           <t>Opex</t>
         </is>
       </c>
-      <c r="S7" s="27" t="n">
+      <c r="S7" s="29" t="n">
         <v>46023.5</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" s="12" t="inlineStr">
         <is>
           <t>SAMPLE</t>
         </is>
@@ -62431,7 +62514,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>SAMPLE-PLANT</t>
         </is>
       </c>
       <c r="G2" s="12" t="inlineStr">
@@ -62466,7 +62549,7 @@
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>85366990</t>
+          <t>SAMPLE-HSN</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
@@ -62474,7 +62557,7 @@
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="O2" s="28" t="n">
+      <c r="O2" s="30" t="n">
         <v>46282.5</v>
       </c>
     </row>
